--- a/outputs/daily/hr_rankings_2026-06-13_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-06-13_full.xlsx
@@ -3300,7 +3300,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>62.8</v>
+        <v>62.6</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>39.7</v>
       </c>
       <c r="R11" t="n">
-        <v>68.90000000000001</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="S11" t="n">
         <v>93.2</v>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -8016,7 +8016,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>58.4</v>
+        <v>58.3</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>33.1</v>
       </c>
       <c r="R28" t="n">
-        <v>68.90000000000001</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="S28" t="n">
         <v>96.59999999999999</v>
@@ -8231,7 +8231,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BI28" t="inlineStr">
@@ -8296,7 +8296,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>58.4</v>
+        <v>58.2</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
         <v>33.1</v>
       </c>
       <c r="R29" t="n">
-        <v>68.90000000000001</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="S29" t="n">
         <v>94.90000000000001</v>
@@ -8511,7 +8511,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BI29" t="inlineStr">
@@ -9919,27 +9919,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>682987</t>
+          <t>701398</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spencer Jones</t>
+          <t>Sal Stewart</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-13T19:07:00Z</t>
+          <t>2026-06-13T20:10:00Z</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9949,17 +9949,17 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Kevin Gausman</t>
+          <t>Michael Soroka</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>592332</t>
+          <t>647336</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -9982,26 +9982,26 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>49.9</v>
+        <v>61.7</v>
       </c>
       <c r="Q35" t="n">
-        <v>39.7</v>
+        <v>33.9</v>
       </c>
       <c r="R35" t="n">
-        <v>68.90000000000001</v>
+        <v>61.3</v>
       </c>
       <c r="S35" t="n">
-        <v>76.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T35" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U35" t="n">
-        <v>58.7</v>
+        <v>28.1</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -10036,7 +10036,7 @@
       <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr"/>
@@ -10053,12 +10053,12 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -10068,12 +10068,12 @@
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Contact streak: 7/18 over last 7 games</t>
+          <t>Last 7 games: 5/27, 1 HR</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.4% barrel, 12.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.6% barrel, 7.8 HR allowed</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
@@ -10083,112 +10083,112 @@
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>15.66</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>44.17</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>92.04</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>105.6184</t>
+          <t>101.5658</t>
         </is>
       </c>
       <c r="AR35" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.5189</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>0.253</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr">
         <is>
-          <t>0.283</t>
+          <t>0.3714</t>
         </is>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>72.24</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>26.65</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>36.68</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>30.83</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>0.2291</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>8.36</t>
+          <t>7.61</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>38.81</t>
+          <t>35.43</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>88.46</t>
+          <t>88.15</t>
         </is>
       </c>
       <c r="BD35" t="inlineStr">
         <is>
-          <t>0.3993</t>
+          <t>0.3895</t>
         </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
-          <t>0.1592</t>
+          <t>0.1497</t>
         </is>
       </c>
       <c r="BF35" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>27.8</t>
         </is>
       </c>
       <c r="BG35" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BI35" t="inlineStr">
         <is>
-          <t>Rogers Centre</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BJ35" t="inlineStr"/>
@@ -10199,27 +10199,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>701398</t>
+          <t>682987</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sal Stewart</t>
+          <t>Spencer Jones</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-13T20:10:00Z</t>
+          <t>2026-06-13T19:07:00Z</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -10229,17 +10229,17 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Michael Soroka</t>
+          <t>Kevin Gausman</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>647336</t>
+          <t>592332</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -10248,7 +10248,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>57.1</v>
+        <v>57</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -10262,26 +10262,26 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>61.7</v>
+        <v>49.9</v>
       </c>
       <c r="Q36" t="n">
-        <v>33.9</v>
+        <v>39.7</v>
       </c>
       <c r="R36" t="n">
-        <v>61.3</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="S36" t="n">
-        <v>96.59999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="T36" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U36" t="n">
-        <v>28.1</v>
+        <v>58.7</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
@@ -10295,7 +10295,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -10316,7 +10316,7 @@
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr"/>
@@ -10333,12 +10333,12 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
@@ -10348,12 +10348,12 @@
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/27, 1 HR</t>
+          <t>Contact streak: 7/18 over last 7 games</t>
         </is>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.6% barrel, 7.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.4% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
@@ -10363,112 +10363,112 @@
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>15.66</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>44.17</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>92.04</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="AQ36" t="inlineStr">
         <is>
-          <t>101.5658</t>
+          <t>105.6184</t>
         </is>
       </c>
       <c r="AR36" t="inlineStr">
         <is>
-          <t>0.5189</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>0.159</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr">
         <is>
-          <t>0.3714</t>
+          <t>0.283</t>
         </is>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>72.24</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>26.65</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>36.68</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>30.83</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>0.2291</t>
+          <t>0.105</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>7.61</t>
+          <t>8.36</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>35.43</t>
+          <t>38.81</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>88.15</t>
+          <t>88.46</t>
         </is>
       </c>
       <c r="BD36" t="inlineStr">
         <is>
-          <t>0.3895</t>
+          <t>0.3993</t>
         </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
-          <t>0.1497</t>
+          <t>0.1592</t>
         </is>
       </c>
       <c r="BF36" t="inlineStr">
         <is>
-          <t>27.8</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="BG36" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BI36" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Rogers Centre</t>
         </is>
       </c>
       <c r="BJ36" t="inlineStr"/>
@@ -14436,7 +14436,7 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>55.4</v>
+        <v>55.3</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -14460,7 +14460,7 @@
         <v>39.7</v>
       </c>
       <c r="R51" t="n">
-        <v>68.90000000000001</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="S51" t="n">
         <v>96.59999999999999</v>
@@ -14651,7 +14651,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BI51" t="inlineStr">
@@ -15227,27 +15227,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>665862</t>
+          <t>702616</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jazz Chisholm Jr.</t>
+          <t>Jackson Holliday</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-13T19:07:00Z</t>
+          <t>2026-06-13T20:05:00Z</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -15257,17 +15257,17 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Kevin Gausman</t>
+          <t>Randy Vásquez</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>592332</t>
+          <t>681190</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -15294,22 +15294,22 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>40.8</v>
+        <v>45.6</v>
       </c>
       <c r="Q54" t="n">
-        <v>39.7</v>
+        <v>69.5</v>
       </c>
       <c r="R54" t="n">
-        <v>68.90000000000001</v>
+        <v>47.6</v>
       </c>
       <c r="S54" t="n">
-        <v>86.40000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T54" t="n">
         <v>80</v>
       </c>
       <c r="U54" t="n">
-        <v>43.7</v>
+        <v>28.9</v>
       </c>
       <c r="V54" t="inlineStr">
         <is>
@@ -15318,30 +15318,34 @@
       </c>
       <c r="W54" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
+      <c r="Z54" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr"/>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>RotoWire not confirmed; order MLB 8 vs RotoWire 9</t>
+        </is>
+      </c>
       <c r="AC54" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -15366,22 +15370,22 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AL54" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.4% barrel, 12.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 12.7% barrel, 11.8 HR allowed</t>
         </is>
       </c>
       <c r="AM54" t="inlineStr">
@@ -15391,112 +15395,112 @@
       </c>
       <c r="AN54" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>12.98</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>40.92</t>
+          <t>42.69</t>
         </is>
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>89.63</t>
+          <t>88.87</t>
         </is>
       </c>
       <c r="AQ54" t="inlineStr">
         <is>
-          <t>100.103</t>
+          <t>99.7498</t>
         </is>
       </c>
       <c r="AR54" t="inlineStr">
         <is>
-          <t>0.3984</t>
+          <t>0.4341</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr">
         <is>
-          <t>0.1791</t>
+          <t>0.1952</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr">
         <is>
-          <t>0.3096</t>
+          <t>0.3336</t>
         </is>
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>70.46</t>
         </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
-          <t>32.59</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>52.05</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>31.03</t>
+          <t>31.89</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>15.6</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>0.1928</t>
+          <t>0.1694</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>8.36</t>
+          <t>12.72</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
         <is>
-          <t>38.81</t>
+          <t>44.69</t>
         </is>
       </c>
       <c r="BC54" t="inlineStr">
         <is>
-          <t>88.46</t>
+          <t>90.64</t>
         </is>
       </c>
       <c r="BD54" t="inlineStr">
         <is>
-          <t>0.3993</t>
+          <t>0.5286</t>
         </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
-          <t>0.1592</t>
+          <t>0.2378</t>
         </is>
       </c>
       <c r="BF54" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>29.51</t>
         </is>
       </c>
       <c r="BG54" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI54" t="inlineStr">
         <is>
-          <t>Rogers Centre</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ54" t="inlineStr"/>
@@ -15507,52 +15511,52 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>702616</t>
+          <t>691016</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jackson Holliday</t>
+          <t>Tyler Soderstrom</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-13T20:05:00Z</t>
+          <t>2026-06-14T02:05:00Z</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Randy Vásquez</t>
+          <t>Kyle Freeland</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>681190</t>
+          <t>607536</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L55" t="n">
@@ -15570,60 +15574,60 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>45.6</v>
+        <v>46.7</v>
       </c>
       <c r="Q55" t="n">
-        <v>69.5</v>
+        <v>59.2</v>
       </c>
       <c r="R55" t="n">
-        <v>47.6</v>
+        <v>27.6</v>
       </c>
       <c r="S55" t="n">
-        <v>52.4</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T55" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U55" t="n">
-        <v>28.9</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="V55" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
+      <c r="Z55" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>RotoWire not confirmed; order MLB 8 vs RotoWire 9</t>
+          <t>lineup projected / unconfirmed</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -15645,27 +15649,27 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL55" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 12.7% barrel, 11.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.6% barrel, 15.7 HR allowed</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
@@ -15675,112 +15679,104 @@
       </c>
       <c r="AN55" t="inlineStr">
         <is>
-          <t>12.98</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>42.69</t>
+          <t>46.51</t>
         </is>
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>88.87</t>
+          <t>90.41</t>
         </is>
       </c>
       <c r="AQ55" t="inlineStr">
         <is>
-          <t>99.7498</t>
+          <t>101.9879</t>
         </is>
       </c>
       <c r="AR55" t="inlineStr">
         <is>
-          <t>0.4341</t>
+          <t>0.4332</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr">
         <is>
-          <t>0.1952</t>
+          <t>0.1827</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr">
         <is>
-          <t>0.3336</t>
+          <t>0.3361</t>
         </is>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>70.46</t>
+          <t>74.14</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>40.63</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>36.07</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>31.89</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>0.1694</t>
+          <t>0.2148</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>12.72</t>
+          <t>9.61</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>44.69</t>
+          <t>45.06</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
         <is>
-          <t>90.64</t>
+          <t>90.89</t>
         </is>
       </c>
       <c r="BD55" t="inlineStr">
         <is>
-          <t>0.5286</t>
+          <t>0.5038</t>
         </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
-          <t>0.2378</t>
+          <t>0.2001</t>
         </is>
       </c>
       <c r="BF55" t="inlineStr">
         <is>
-          <t>29.51</t>
-        </is>
-      </c>
-      <c r="BG55" t="inlineStr">
-        <is>
-          <t>In From LF</t>
-        </is>
-      </c>
-      <c r="BH55" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
+          <t>28.66</t>
+        </is>
+      </c>
+      <c r="BG55" t="inlineStr"/>
+      <c r="BH55" t="inlineStr"/>
       <c r="BI55" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Las Vegas Ballpark</t>
         </is>
       </c>
       <c r="BJ55" t="inlineStr"/>
@@ -15791,56 +15787,56 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>691016</t>
+          <t>680776</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Tyler Soderstrom</t>
+          <t>Jarren Duran</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-14T02:05:00Z</t>
+          <t>2026-06-13T20:10:00Z</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Kyle Freeland</t>
+          <t>Jacob deGrom</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>607536</t>
+          <t>594798</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>54.8</v>
+        <v>54.7</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
@@ -15854,62 +15850,58 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>46.7</v>
+        <v>41.1</v>
       </c>
       <c r="Q56" t="n">
-        <v>59.2</v>
+        <v>55.3</v>
       </c>
       <c r="R56" t="n">
-        <v>27.6</v>
+        <v>56.2</v>
       </c>
       <c r="S56" t="n">
-        <v>90.40000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T56" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U56" t="n">
-        <v>77.90000000000001</v>
+        <v>2.7</v>
       </c>
       <c r="V56" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr"/>
       <c r="AC56" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -15929,134 +15921,142 @@
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 4/29, 0 HR</t>
         </is>
       </c>
       <c r="AL56" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.6% barrel, 15.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.1% barrel, 16.9 HR allowed</t>
         </is>
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN56" t="inlineStr">
         <is>
-          <t>11.05</t>
+          <t>10.68</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>46.51</t>
+          <t>41.97</t>
         </is>
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>90.41</t>
+          <t>90.82</t>
         </is>
       </c>
       <c r="AQ56" t="inlineStr">
         <is>
-          <t>101.9879</t>
+          <t>102.2729</t>
         </is>
       </c>
       <c r="AR56" t="inlineStr">
         <is>
-          <t>0.4332</t>
+          <t>0.3904</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr">
         <is>
-          <t>0.1827</t>
+          <t>0.1564</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr">
         <is>
-          <t>0.3361</t>
+          <t>0.3029</t>
         </is>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>74.14</t>
+          <t>75.15</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>40.63</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>36.07</t>
+          <t>40.58</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>22.51</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>0.2148</t>
+          <t>0.1748</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>9.61</t>
+          <t>10.07</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>45.06</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
         <is>
-          <t>90.89</t>
+          <t>90.87</t>
         </is>
       </c>
       <c r="BD56" t="inlineStr">
         <is>
-          <t>0.5038</t>
+          <t>0.4134</t>
         </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
-          <t>0.2001</t>
+          <t>0.1826</t>
         </is>
       </c>
       <c r="BF56" t="inlineStr">
         <is>
-          <t>28.66</t>
-        </is>
-      </c>
-      <c r="BG56" t="inlineStr"/>
-      <c r="BH56" t="inlineStr"/>
+          <t>32.12</t>
+        </is>
+      </c>
+      <c r="BG56" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH56" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI56" t="inlineStr">
         <is>
-          <t>Las Vegas Ballpark</t>
+          <t>Fenway Park</t>
         </is>
       </c>
       <c r="BJ56" t="inlineStr"/>
@@ -16067,27 +16067,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>680776</t>
+          <t>665862</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jarren Duran</t>
+          <t>Jazz Chisholm Jr.</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-13T20:10:00Z</t>
+          <t>2026-06-13T19:07:00Z</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -16102,12 +16102,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Jacob deGrom</t>
+          <t>Kevin Gausman</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>594798</t>
+          <t>592332</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -16116,7 +16116,7 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>54.7</v>
+        <v>54.6</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
@@ -16134,13 +16134,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>41.1</v>
+        <v>40.8</v>
       </c>
       <c r="Q57" t="n">
-        <v>55.3</v>
+        <v>39.7</v>
       </c>
       <c r="R57" t="n">
-        <v>56.2</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="S57" t="n">
         <v>86.40000000000001</v>
@@ -16149,7 +16149,7 @@
         <v>80</v>
       </c>
       <c r="U57" t="n">
-        <v>2.7</v>
+        <v>43.7</v>
       </c>
       <c r="V57" t="inlineStr">
         <is>
@@ -16206,137 +16206,137 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/29, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL57" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.1% barrel, 16.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.4% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN57" t="inlineStr">
         <is>
-          <t>10.68</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>41.97</t>
+          <t>40.92</t>
         </is>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>90.82</t>
+          <t>89.63</t>
         </is>
       </c>
       <c r="AQ57" t="inlineStr">
         <is>
-          <t>102.2729</t>
+          <t>100.103</t>
         </is>
       </c>
       <c r="AR57" t="inlineStr">
         <is>
-          <t>0.3904</t>
+          <t>0.3984</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr">
         <is>
-          <t>0.1564</t>
+          <t>0.1791</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr">
         <is>
-          <t>0.3029</t>
+          <t>0.3096</t>
         </is>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>75.15</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>32.59</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>40.58</t>
+          <t>52.05</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>22.51</t>
+          <t>31.03</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>15.6</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>0.1748</t>
+          <t>0.1928</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>10.07</t>
+          <t>8.36</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>38.81</t>
         </is>
       </c>
       <c r="BC57" t="inlineStr">
         <is>
-          <t>90.87</t>
+          <t>88.46</t>
         </is>
       </c>
       <c r="BD57" t="inlineStr">
         <is>
-          <t>0.4134</t>
+          <t>0.3993</t>
         </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
-          <t>0.1826</t>
+          <t>0.1592</t>
         </is>
       </c>
       <c r="BF57" t="inlineStr">
         <is>
-          <t>32.12</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="BG57" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BI57" t="inlineStr">
         <is>
-          <t>Fenway Park</t>
+          <t>Rogers Centre</t>
         </is>
       </c>
       <c r="BJ57" t="inlineStr"/>
@@ -18352,7 +18352,7 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>53.9</v>
+        <v>53.8</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
@@ -18376,7 +18376,7 @@
         <v>39.7</v>
       </c>
       <c r="R65" t="n">
-        <v>68.90000000000001</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="S65" t="n">
         <v>94.90000000000001</v>
@@ -18567,7 +18567,7 @@
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BI65" t="inlineStr">
@@ -19411,47 +19411,47 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>641857</t>
+          <t>686611</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ryan McMahon</t>
+          <t>Dylan Crews</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-13T19:07:00Z</t>
+          <t>2026-06-13T20:05:00Z</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Kevin Gausman</t>
+          <t>Luis Castillo</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>592332</t>
+          <t>622491</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -19474,58 +19474,62 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>50.1</v>
+        <v>46.2</v>
       </c>
       <c r="Q69" t="n">
-        <v>39.7</v>
+        <v>57.8</v>
       </c>
       <c r="R69" t="n">
-        <v>68.90000000000001</v>
+        <v>28.2</v>
       </c>
       <c r="S69" t="n">
-        <v>52.4</v>
+        <v>95.5</v>
       </c>
       <c r="T69" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U69" t="n">
-        <v>47.2</v>
+        <v>41.7</v>
       </c>
       <c r="V69" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W69" t="inlineStr">
+      <c r="Z69" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X69" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC69" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -19545,27 +19549,27 @@
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/16, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL69" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.4% barrel, 12.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.8% barrel, 12.5 HR allowed</t>
         </is>
       </c>
       <c r="AM69" t="inlineStr">
@@ -19575,112 +19579,104 @@
       </c>
       <c r="AN69" t="inlineStr">
         <is>
-          <t>11.19</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>50.78</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>91.69</t>
+          <t>91.03</t>
         </is>
       </c>
       <c r="AQ69" t="inlineStr">
         <is>
-          <t>102.2341</t>
+          <t>101.8356</t>
         </is>
       </c>
       <c r="AR69" t="inlineStr">
         <is>
-          <t>0.398</t>
+          <t>0.4476</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr">
         <is>
-          <t>0.1765</t>
+          <t>0.1916</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr">
         <is>
-          <t>0.3024</t>
+          <t>0.3287</t>
         </is>
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>74.49</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
-          <t>47.17</t>
+          <t>36.93</t>
         </is>
       </c>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>37.35</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>32.94</t>
+          <t>27.63</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>0.1537</t>
+          <t>0.1377</t>
         </is>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>8.36</t>
+          <t>10.82</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
         <is>
-          <t>38.81</t>
+          <t>47.03</t>
         </is>
       </c>
       <c r="BC69" t="inlineStr">
         <is>
-          <t>88.46</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="BD69" t="inlineStr">
         <is>
-          <t>0.3993</t>
+          <t>0.439</t>
         </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
-          <t>0.1592</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="BF69" t="inlineStr">
         <is>
-          <t>25.88</t>
-        </is>
-      </c>
-      <c r="BG69" t="inlineStr">
-        <is>
-          <t>Out To RF</t>
-        </is>
-      </c>
-      <c r="BH69" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
+          <t>28.21</t>
+        </is>
+      </c>
+      <c r="BG69" t="inlineStr"/>
+      <c r="BH69" t="inlineStr"/>
       <c r="BI69" t="inlineStr">
         <is>
-          <t>Rogers Centre</t>
+          <t>Nationals Park</t>
         </is>
       </c>
       <c r="BJ69" t="inlineStr"/>
@@ -19691,47 +19687,47 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>686611</t>
+          <t>641857</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Dylan Crews</t>
+          <t>Ryan McMahon</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-13T20:05:00Z</t>
+          <t>2026-06-13T19:07:00Z</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Luis Castillo</t>
+          <t>Kevin Gausman</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>622491</t>
+          <t>592332</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -19740,7 +19736,7 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>53.3</v>
+        <v>53.1</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
@@ -19754,62 +19750,58 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>46.2</v>
+        <v>50.1</v>
       </c>
       <c r="Q70" t="n">
-        <v>57.8</v>
+        <v>39.7</v>
       </c>
       <c r="R70" t="n">
-        <v>28.2</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="S70" t="n">
-        <v>95.5</v>
+        <v>52.4</v>
       </c>
       <c r="T70" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U70" t="n">
-        <v>41.7</v>
+        <v>47.2</v>
       </c>
       <c r="V70" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X70" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr"/>
       <c r="AC70" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -19829,27 +19821,27 @@
       </c>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/16, 1 HR</t>
         </is>
       </c>
       <c r="AL70" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.8% barrel, 12.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.4% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM70" t="inlineStr">
@@ -19859,104 +19851,112 @@
       </c>
       <c r="AN70" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>11.19</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>50.78</t>
         </is>
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>91.03</t>
+          <t>91.69</t>
         </is>
       </c>
       <c r="AQ70" t="inlineStr">
         <is>
-          <t>101.8356</t>
+          <t>102.2341</t>
         </is>
       </c>
       <c r="AR70" t="inlineStr">
         <is>
-          <t>0.4476</t>
+          <t>0.398</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr">
         <is>
-          <t>0.1916</t>
+          <t>0.1765</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr">
         <is>
-          <t>0.3287</t>
+          <t>0.3024</t>
         </is>
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>74.49</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
-          <t>36.93</t>
+          <t>47.17</t>
         </is>
       </c>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>37.35</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>27.63</t>
+          <t>32.94</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>0.1377</t>
+          <t>0.1537</t>
         </is>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>10.82</t>
+          <t>8.36</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
         <is>
-          <t>47.03</t>
+          <t>38.81</t>
         </is>
       </c>
       <c r="BC70" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>88.46</t>
         </is>
       </c>
       <c r="BD70" t="inlineStr">
         <is>
-          <t>0.439</t>
+          <t>0.3993</t>
         </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.1592</t>
         </is>
       </c>
       <c r="BF70" t="inlineStr">
         <is>
-          <t>28.21</t>
-        </is>
-      </c>
-      <c r="BG70" t="inlineStr"/>
-      <c r="BH70" t="inlineStr"/>
+          <t>25.88</t>
+        </is>
+      </c>
+      <c r="BG70" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH70" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI70" t="inlineStr">
         <is>
-          <t>Nationals Park</t>
+          <t>Rogers Centre</t>
         </is>
       </c>
       <c r="BJ70" t="inlineStr"/>
@@ -20531,27 +20531,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>678218</t>
+          <t>663330</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Brandon Valenzuela</t>
+          <t>Jahmai Jones</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-06-13T19:07:00Z</t>
+          <t>2026-06-13T20:10:00Z</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -20561,22 +20561,22 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Cam Schlittler</t>
+          <t>Joey Cantillo</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>693645</t>
+          <t>676282</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L73" t="n">
@@ -20594,61 +20594,65 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P73" t="n">
-        <v>38.1</v>
+        <v>48.8</v>
       </c>
       <c r="Q73" t="n">
-        <v>32.5</v>
+        <v>42</v>
       </c>
       <c r="R73" t="n">
-        <v>68.90000000000001</v>
+        <v>53.6</v>
       </c>
       <c r="S73" t="n">
-        <v>76.2</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T73" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U73" t="n">
-        <v>91.5</v>
+        <v>0</v>
       </c>
       <c r="V73" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W73" t="inlineStr">
+      <c r="Z73" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X73" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD73" t="inlineStr"/>
@@ -20665,142 +20669,142 @@
       </c>
       <c r="AH73" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 0/11, 0 HR</t>
         </is>
       </c>
       <c r="AL73" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 7.4% barrel, 5.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN73" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>47.79</t>
         </is>
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>91.29</t>
         </is>
       </c>
       <c r="AQ73" t="inlineStr">
         <is>
-          <t>99.4131</t>
+          <t>102.0909</t>
         </is>
       </c>
       <c r="AR73" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.449</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>0.1954</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr">
         <is>
-          <t>0.349</t>
+          <t>0.3423</t>
         </is>
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>72.97</t>
         </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>32.98</t>
         </is>
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>47.66</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>29.88</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>0.1503</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>8.74</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
         <is>
-          <t>40.97</t>
+          <t>38.93</t>
         </is>
       </c>
       <c r="BC73" t="inlineStr">
         <is>
-          <t>88.58</t>
+          <t>88.52</t>
         </is>
       </c>
       <c r="BD73" t="inlineStr">
         <is>
-          <t>0.3567</t>
+          <t>0.3994</t>
         </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
-          <t>0.1344</t>
+          <t>0.1634</t>
         </is>
       </c>
       <c r="BF73" t="inlineStr">
         <is>
-          <t>27.02</t>
+          <t>30.87</t>
         </is>
       </c>
       <c r="BG73" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BI73" t="inlineStr">
         <is>
-          <t>Rogers Centre</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ73" t="inlineStr"/>
@@ -20811,27 +20815,27 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>663330</t>
+          <t>678218</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Jahmai Jones</t>
+          <t>Brandon Valenzuela</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-06-13T20:10:00Z</t>
+          <t>2026-06-13T19:07:00Z</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -20841,26 +20845,26 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Joey Cantillo</t>
+          <t>Cam Schlittler</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>676282</t>
+          <t>693645</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>52.7</v>
+        <v>52.6</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
@@ -20874,65 +20878,61 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>48.8</v>
+        <v>38.1</v>
       </c>
       <c r="Q74" t="n">
-        <v>42</v>
+        <v>32.5</v>
       </c>
       <c r="R74" t="n">
-        <v>53.6</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="S74" t="n">
-        <v>81.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T74" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U74" t="n">
-        <v>0</v>
+        <v>91.5</v>
       </c>
       <c r="V74" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W74" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X74" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y74" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr"/>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD74" t="inlineStr"/>
@@ -20949,142 +20949,142 @@
       </c>
       <c r="AH74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Last 7 games: 0/11, 0 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL74" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 10.7 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.4% barrel, 5.2 HR allowed</t>
         </is>
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN74" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>47.79</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>91.29</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AQ74" t="inlineStr">
         <is>
-          <t>102.0909</t>
+          <t>99.4131</t>
         </is>
       </c>
       <c r="AR74" t="inlineStr">
         <is>
-          <t>0.449</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr">
         <is>
-          <t>0.1954</t>
+          <t>0.186</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr">
         <is>
-          <t>0.3423</t>
+          <t>0.349</t>
         </is>
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>72.97</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>32.98</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>47.66</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>29.88</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>0.1503</t>
+          <t>0.205</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>8.74</t>
+          <t>7.36</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
         <is>
-          <t>38.93</t>
+          <t>40.97</t>
         </is>
       </c>
       <c r="BC74" t="inlineStr">
         <is>
-          <t>88.52</t>
+          <t>88.58</t>
         </is>
       </c>
       <c r="BD74" t="inlineStr">
         <is>
-          <t>0.3994</t>
+          <t>0.3567</t>
         </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
-          <t>0.1634</t>
+          <t>0.1344</t>
         </is>
       </c>
       <c r="BF74" t="inlineStr">
         <is>
-          <t>30.87</t>
+          <t>27.02</t>
         </is>
       </c>
       <c r="BG74" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BI74" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Rogers Centre</t>
         </is>
       </c>
       <c r="BJ74" t="inlineStr"/>
@@ -24748,7 +24748,7 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>50.9</v>
+        <v>50.7</v>
       </c>
       <c r="M88" t="inlineStr">
         <is>
@@ -24772,7 +24772,7 @@
         <v>33.1</v>
       </c>
       <c r="R88" t="n">
-        <v>68.90000000000001</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="S88" t="n">
         <v>93.2</v>
@@ -24963,7 +24963,7 @@
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BI88" t="inlineStr">
@@ -26140,7 +26140,7 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
       <c r="M93" t="inlineStr">
         <is>
@@ -26164,7 +26164,7 @@
         <v>38.3</v>
       </c>
       <c r="R93" t="n">
-        <v>68.90000000000001</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="S93" t="n">
         <v>100</v>
@@ -26355,7 +26355,7 @@
       </c>
       <c r="BH93" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BI93" t="inlineStr">
@@ -29375,27 +29375,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>682818</t>
+          <t>687221</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Yohendrick Piñango</t>
+          <t>Dalton Rushing</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-06-13T19:07:00Z</t>
+          <t>2026-06-13T20:10:00Z</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -29405,17 +29405,17 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Cam Schlittler</t>
+          <t>Sean Burke</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>693645</t>
+          <t>680732</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -29438,61 +29438,65 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P105" t="n">
-        <v>38.4</v>
+        <v>42.4</v>
       </c>
       <c r="Q105" t="n">
-        <v>33.1</v>
+        <v>39.6</v>
       </c>
       <c r="R105" t="n">
-        <v>68.90000000000001</v>
+        <v>59.6</v>
       </c>
       <c r="S105" t="n">
-        <v>64.3</v>
+        <v>47.9</v>
       </c>
       <c r="T105" t="n">
         <v>80</v>
       </c>
       <c r="U105" t="n">
-        <v>39.5</v>
+        <v>54.3</v>
       </c>
       <c r="V105" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W105" t="inlineStr">
+      <c r="Z105" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X105" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y105" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD105" t="inlineStr"/>
@@ -29509,12 +29513,12 @@
       </c>
       <c r="AH105" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ105" t="inlineStr">
@@ -29524,12 +29528,12 @@
       </c>
       <c r="AK105" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/23, 1 HR</t>
+          <t>Contact streak: 9/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL105" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.4% barrel, 5.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.8% barrel, 11.8 HR allowed</t>
         </is>
       </c>
       <c r="AM105" t="inlineStr">
@@ -29539,112 +29543,112 @@
       </c>
       <c r="AN105" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>11.06</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>41.73</t>
         </is>
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>89.05</t>
         </is>
       </c>
       <c r="AQ105" t="inlineStr">
         <is>
-          <t>102.1842</t>
+          <t>101.2084</t>
         </is>
       </c>
       <c r="AR105" t="inlineStr">
         <is>
-          <t>0.422</t>
+          <t>0.4413</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>0.1879</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr">
         <is>
-          <t>0.321</t>
+          <t>0.3397</t>
         </is>
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>72.61</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>47.26</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>0.2173</t>
         </is>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>7.77</t>
         </is>
       </c>
       <c r="BB105" t="inlineStr">
         <is>
-          <t>40.97</t>
+          <t>38.15</t>
         </is>
       </c>
       <c r="BC105" t="inlineStr">
         <is>
-          <t>88.58</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BD105" t="inlineStr">
         <is>
-          <t>0.3567</t>
+          <t>0.3961</t>
         </is>
       </c>
       <c r="BE105" t="inlineStr">
         <is>
-          <t>0.1344</t>
+          <t>0.1557</t>
         </is>
       </c>
       <c r="BF105" t="inlineStr">
         <is>
-          <t>27.02</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="BG105" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH105" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BI105" t="inlineStr">
         <is>
-          <t>Rogers Centre</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ105" t="inlineStr"/>
@@ -29655,27 +29659,27 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>687221</t>
+          <t>682818</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Dalton Rushing</t>
+          <t>Yohendrick Piñango</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-06-13T20:10:00Z</t>
+          <t>2026-06-13T19:07:00Z</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -29685,17 +29689,17 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Sean Burke</t>
+          <t>Cam Schlittler</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>680732</t>
+          <t>693645</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -29704,7 +29708,7 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
       <c r="M106" t="inlineStr">
         <is>
@@ -29718,65 +29722,61 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P106" t="n">
-        <v>42.4</v>
+        <v>38.4</v>
       </c>
       <c r="Q106" t="n">
-        <v>39.6</v>
+        <v>33.1</v>
       </c>
       <c r="R106" t="n">
-        <v>59.6</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="S106" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T106" t="n">
         <v>80</v>
       </c>
       <c r="U106" t="n">
-        <v>54.3</v>
+        <v>39.5</v>
       </c>
       <c r="V106" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X106" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W106" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X106" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y106" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr"/>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD106" t="inlineStr"/>
@@ -29793,12 +29793,12 @@
       </c>
       <c r="AH106" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ106" t="inlineStr">
@@ -29808,12 +29808,12 @@
       </c>
       <c r="AK106" t="inlineStr">
         <is>
-          <t>Contact streak: 9/25 over last 7 games</t>
+          <t>Last 7 games: 6/23, 1 HR</t>
         </is>
       </c>
       <c r="AL106" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.8% barrel, 11.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.4% barrel, 5.2 HR allowed</t>
         </is>
       </c>
       <c r="AM106" t="inlineStr">
@@ -29823,112 +29823,112 @@
       </c>
       <c r="AN106" t="inlineStr">
         <is>
-          <t>11.06</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>41.73</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>89.05</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AQ106" t="inlineStr">
         <is>
-          <t>101.2084</t>
+          <t>102.1842</t>
         </is>
       </c>
       <c r="AR106" t="inlineStr">
         <is>
-          <t>0.4413</t>
+          <t>0.422</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr">
         <is>
-          <t>0.1879</t>
+          <t>0.141</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr">
         <is>
-          <t>0.3397</t>
+          <t>0.321</t>
         </is>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>72.61</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>47.26</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>0.2173</t>
+          <t>0.147</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>7.77</t>
+          <t>7.36</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
-          <t>38.15</t>
+          <t>40.97</t>
         </is>
       </c>
       <c r="BC106" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>88.58</t>
         </is>
       </c>
       <c r="BD106" t="inlineStr">
         <is>
-          <t>0.3961</t>
+          <t>0.3567</t>
         </is>
       </c>
       <c r="BE106" t="inlineStr">
         <is>
-          <t>0.1557</t>
+          <t>0.1344</t>
         </is>
       </c>
       <c r="BF106" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>27.02</t>
         </is>
       </c>
       <c r="BG106" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH106" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BI106" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Rogers Centre</t>
         </is>
       </c>
       <c r="BJ106" t="inlineStr"/>
@@ -42467,27 +42467,27 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>807727</t>
+          <t>553993</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Charles McAdoo</t>
+          <t>Eugenio Suárez</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-06-13T19:07:00Z</t>
+          <t>2026-06-13T20:10:00Z</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -42497,17 +42497,17 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Cam Schlittler</t>
+          <t>Michael Soroka</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>693645</t>
+          <t>647336</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -42534,22 +42534,22 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>38.7</v>
+        <v>31.1</v>
       </c>
       <c r="Q152" t="n">
-        <v>33.1</v>
+        <v>33.9</v>
       </c>
       <c r="R152" t="n">
-        <v>68.90000000000001</v>
+        <v>61.3</v>
       </c>
       <c r="S152" t="n">
-        <v>52.4</v>
+        <v>76.2</v>
       </c>
       <c r="T152" t="n">
         <v>50</v>
       </c>
       <c r="U152" t="n">
-        <v>28.5</v>
+        <v>31.4</v>
       </c>
       <c r="V152" t="inlineStr">
         <is>
@@ -42563,7 +42563,7 @@
       </c>
       <c r="X152" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y152" t="inlineStr">
@@ -42584,7 +42584,7 @@
       <c r="AB152" t="inlineStr"/>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD152" t="inlineStr"/>
@@ -42596,17 +42596,17 @@
       </c>
       <c r="AG152" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ152" t="inlineStr">
@@ -42616,12 +42616,12 @@
       </c>
       <c r="AK152" t="inlineStr">
         <is>
-          <t>Last 5 games: 3/16, 1 HR</t>
+          <t>Last 7 games: 6/29, 1 HR</t>
         </is>
       </c>
       <c r="AL152" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.4% barrel, 5.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.6% barrel, 7.8 HR allowed</t>
         </is>
       </c>
       <c r="AM152" t="inlineStr">
@@ -42631,112 +42631,112 @@
       </c>
       <c r="AN152" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>33.67</t>
         </is>
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>87.61</t>
         </is>
       </c>
       <c r="AQ152" t="inlineStr">
         <is>
-          <t>98.5074</t>
+          <t>99.1737</t>
         </is>
       </c>
       <c r="AR152" t="inlineStr">
         <is>
-          <t>0.374</t>
+          <t>0.3804</t>
         </is>
       </c>
       <c r="AS152" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>0.1652</t>
         </is>
       </c>
       <c r="AT152" t="inlineStr">
         <is>
-          <t>0.255</t>
+          <t>0.2927</t>
         </is>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>71.53</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>18.24</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
+          <t>46.77</t>
+        </is>
+      </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>28.93</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr">
+        <is>
           <t>18.2</t>
         </is>
       </c>
-      <c r="AX152" t="inlineStr">
-        <is>
-          <t>27.3</t>
-        </is>
-      </c>
-      <c r="AY152" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>0.1867</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>7.61</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
-          <t>40.97</t>
+          <t>35.43</t>
         </is>
       </c>
       <c r="BC152" t="inlineStr">
         <is>
-          <t>88.58</t>
+          <t>88.15</t>
         </is>
       </c>
       <c r="BD152" t="inlineStr">
         <is>
-          <t>0.3567</t>
+          <t>0.3895</t>
         </is>
       </c>
       <c r="BE152" t="inlineStr">
         <is>
-          <t>0.1344</t>
+          <t>0.1497</t>
         </is>
       </c>
       <c r="BF152" t="inlineStr">
         <is>
-          <t>27.02</t>
+          <t>27.8</t>
         </is>
       </c>
       <c r="BG152" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH152" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BI152" t="inlineStr">
         <is>
-          <t>Rogers Centre</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BJ152" t="inlineStr"/>
@@ -42747,47 +42747,47 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>553993</t>
+          <t>691720</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Eugenio Suárez</t>
+          <t>Kyle Karros</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-06-13T20:10:00Z</t>
+          <t>2026-06-14T02:05:00Z</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Michael Soroka</t>
+          <t>Joey Estes</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>647336</t>
+          <t>683155</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -42810,61 +42810,65 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P153" t="n">
-        <v>31.1</v>
+        <v>19.9</v>
       </c>
       <c r="Q153" t="n">
-        <v>33.9</v>
+        <v>58.2</v>
       </c>
       <c r="R153" t="n">
-        <v>61.3</v>
+        <v>27.6</v>
       </c>
       <c r="S153" t="n">
-        <v>76.2</v>
+        <v>95.5</v>
       </c>
       <c r="T153" t="n">
         <v>50</v>
       </c>
       <c r="U153" t="n">
-        <v>31.4</v>
+        <v>34.5</v>
       </c>
       <c r="V153" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W153" t="inlineStr">
+      <c r="Z153" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X153" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y153" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z153" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB153" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2025</t>
         </is>
       </c>
       <c r="AD153" t="inlineStr"/>
@@ -42881,142 +42885,134 @@
       </c>
       <c r="AH153" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/29, 1 HR</t>
+          <t>Contact streak: 7/20 over last 7 games</t>
         </is>
       </c>
       <c r="AL153" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.6% barrel, 7.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.9% barrel, 4.0 HR allowed</t>
         </is>
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN153" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="AO153" t="inlineStr">
         <is>
-          <t>33.67</t>
+          <t>39.16</t>
         </is>
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>87.61</t>
+          <t>88.74</t>
         </is>
       </c>
       <c r="AQ153" t="inlineStr">
         <is>
-          <t>99.1737</t>
+          <t>99.4316</t>
         </is>
       </c>
       <c r="AR153" t="inlineStr">
         <is>
-          <t>0.3804</t>
+          <t>0.3439</t>
         </is>
       </c>
       <c r="AS153" t="inlineStr">
         <is>
-          <t>0.1652</t>
+          <t>0.1033</t>
         </is>
       </c>
       <c r="AT153" t="inlineStr">
         <is>
-          <t>0.2927</t>
+          <t>0.3098</t>
         </is>
       </c>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>71.53</t>
+          <t>69.87</t>
         </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
-          <t>18.24</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>46.77</t>
+          <t>37.68</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>21.33</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>0.1867</t>
+          <t>0.0874</t>
         </is>
       </c>
       <c r="BA153" t="inlineStr">
         <is>
-          <t>7.61</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="BB153" t="inlineStr">
         <is>
-          <t>35.43</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="BC153" t="inlineStr">
         <is>
-          <t>88.15</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="BD153" t="inlineStr">
         <is>
-          <t>0.3895</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="BE153" t="inlineStr">
         <is>
-          <t>0.1497</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="BF153" t="inlineStr">
         <is>
-          <t>27.8</t>
-        </is>
-      </c>
-      <c r="BG153" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH153" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
+          <t>45.2</t>
+        </is>
+      </c>
+      <c r="BG153" t="inlineStr"/>
+      <c r="BH153" t="inlineStr"/>
       <c r="BI153" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Las Vegas Ballpark</t>
         </is>
       </c>
       <c r="BJ153" t="inlineStr"/>
@@ -43027,47 +43023,47 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>691720</t>
+          <t>807727</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Kyle Karros</t>
+          <t>Charles McAdoo</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-06-14T02:05:00Z</t>
+          <t>2026-06-13T19:07:00Z</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Joey Estes</t>
+          <t>Cam Schlittler</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>683155</t>
+          <t>693645</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -43076,7 +43072,7 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>44.3</v>
+        <v>44.1</v>
       </c>
       <c r="M154" t="inlineStr">
         <is>
@@ -43090,65 +43086,61 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P154" t="n">
-        <v>19.9</v>
+        <v>38.7</v>
       </c>
       <c r="Q154" t="n">
-        <v>58.2</v>
+        <v>33.1</v>
       </c>
       <c r="R154" t="n">
-        <v>27.6</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="S154" t="n">
-        <v>95.5</v>
+        <v>52.4</v>
       </c>
       <c r="T154" t="n">
         <v>50</v>
       </c>
       <c r="U154" t="n">
-        <v>34.5</v>
+        <v>28.5</v>
       </c>
       <c r="V154" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X154" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z154" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W154" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X154" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y154" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB154" t="inlineStr"/>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD154" t="inlineStr"/>
@@ -43160,139 +43152,147 @@
       </c>
       <c r="AG154" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI154" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
         <is>
-          <t>Contact streak: 7/20 over last 7 games</t>
+          <t>Last 5 games: 3/16, 1 HR</t>
         </is>
       </c>
       <c r="AL154" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.9% barrel, 4.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.4% barrel, 5.2 HR allowed</t>
         </is>
       </c>
       <c r="AM154" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN154" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="AO154" t="inlineStr">
         <is>
-          <t>39.16</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>88.74</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AQ154" t="inlineStr">
         <is>
-          <t>99.4316</t>
+          <t>98.5074</t>
         </is>
       </c>
       <c r="AR154" t="inlineStr">
         <is>
-          <t>0.3439</t>
+          <t>0.374</t>
         </is>
       </c>
       <c r="AS154" t="inlineStr">
         <is>
-          <t>0.1033</t>
+          <t>0.157</t>
         </is>
       </c>
       <c r="AT154" t="inlineStr">
         <is>
-          <t>0.3098</t>
+          <t>0.255</t>
         </is>
       </c>
       <c r="AU154" t="inlineStr">
         <is>
-          <t>69.87</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>37.68</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>21.33</t>
+          <t>27.3</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>0.0874</t>
+          <t>0.187</t>
         </is>
       </c>
       <c r="BA154" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>7.36</t>
         </is>
       </c>
       <c r="BB154" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>40.97</t>
         </is>
       </c>
       <c r="BC154" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>88.58</t>
         </is>
       </c>
       <c r="BD154" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.3567</t>
         </is>
       </c>
       <c r="BE154" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.1344</t>
         </is>
       </c>
       <c r="BF154" t="inlineStr">
         <is>
-          <t>45.2</t>
-        </is>
-      </c>
-      <c r="BG154" t="inlineStr"/>
-      <c r="BH154" t="inlineStr"/>
+          <t>27.02</t>
+        </is>
+      </c>
+      <c r="BG154" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH154" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI154" t="inlineStr">
         <is>
-          <t>Las Vegas Ballpark</t>
+          <t>Rogers Centre</t>
         </is>
       </c>
       <c r="BJ154" t="inlineStr"/>
@@ -43303,27 +43303,27 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>664770</t>
+          <t>663837</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Nathan Lukes</t>
+          <t>Matt Vierling</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-06-13T19:07:00Z</t>
+          <t>2026-06-13T20:10:00Z</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -43333,22 +43333,22 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Cam Schlittler</t>
+          <t>Joey Cantillo</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>693645</t>
+          <t>676282</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L155" t="n">
@@ -43366,58 +43366,62 @@
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P155" t="n">
-        <v>11.3</v>
+        <v>32</v>
       </c>
       <c r="Q155" t="n">
-        <v>33.1</v>
+        <v>42</v>
       </c>
       <c r="R155" t="n">
-        <v>68.90000000000001</v>
+        <v>53.6</v>
       </c>
       <c r="S155" t="n">
-        <v>100</v>
+        <v>59.8</v>
       </c>
       <c r="T155" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U155" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="V155" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X155" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W155" t="inlineStr">
+      <c r="Z155" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X155" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y155" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z155" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB155" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC155" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -43437,12 +43441,12 @@
       </c>
       <c r="AH155" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI155" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ155" t="inlineStr">
@@ -43452,127 +43456,127 @@
       </c>
       <c r="AK155" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 0 HR</t>
+          <t>Last 7 games: 1/15, 0 HR</t>
         </is>
       </c>
       <c r="AL155" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.4% barrel, 5.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN155" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>8.04</t>
         </is>
       </c>
       <c r="AO155" t="inlineStr">
         <is>
-          <t>33.71</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>86.92</t>
+          <t>88.49</t>
         </is>
       </c>
       <c r="AQ155" t="inlineStr">
         <is>
-          <t>97.5781</t>
+          <t>98.7956</t>
         </is>
       </c>
       <c r="AR155" t="inlineStr">
         <is>
-          <t>0.3717</t>
+          <t>0.4017</t>
         </is>
       </c>
       <c r="AS155" t="inlineStr">
         <is>
-          <t>0.0931</t>
+          <t>0.1531</t>
         </is>
       </c>
       <c r="AT155" t="inlineStr">
         <is>
-          <t>0.3136</t>
+          <t>0.3177</t>
         </is>
       </c>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>67.58</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>33.59</t>
+          <t>33.02</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>18.29</t>
+          <t>32.18</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>0.1184</t>
         </is>
       </c>
       <c r="BA155" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>8.74</t>
         </is>
       </c>
       <c r="BB155" t="inlineStr">
         <is>
-          <t>40.97</t>
+          <t>38.93</t>
         </is>
       </c>
       <c r="BC155" t="inlineStr">
         <is>
-          <t>88.58</t>
+          <t>88.52</t>
         </is>
       </c>
       <c r="BD155" t="inlineStr">
         <is>
-          <t>0.3567</t>
+          <t>0.3994</t>
         </is>
       </c>
       <c r="BE155" t="inlineStr">
         <is>
-          <t>0.1344</t>
+          <t>0.1634</t>
         </is>
       </c>
       <c r="BF155" t="inlineStr">
         <is>
-          <t>27.02</t>
+          <t>30.87</t>
         </is>
       </c>
       <c r="BG155" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH155" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BI155" t="inlineStr">
         <is>
-          <t>Rogers Centre</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ155" t="inlineStr"/>
@@ -43583,27 +43587,27 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>663837</t>
+          <t>664770</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Matt Vierling</t>
+          <t>Nathan Lukes</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-06-13T20:10:00Z</t>
+          <t>2026-06-13T19:07:00Z</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -43613,26 +43617,26 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Joey Cantillo</t>
+          <t>Cam Schlittler</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>676282</t>
+          <t>693645</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L156" t="n">
-        <v>44.1</v>
+        <v>44</v>
       </c>
       <c r="M156" t="inlineStr">
         <is>
@@ -43646,62 +43650,58 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P156" t="n">
-        <v>32</v>
+        <v>11.3</v>
       </c>
       <c r="Q156" t="n">
-        <v>42</v>
+        <v>33.1</v>
       </c>
       <c r="R156" t="n">
-        <v>53.6</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="S156" t="n">
-        <v>59.8</v>
+        <v>100</v>
       </c>
       <c r="T156" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U156" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="V156" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X156" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z156" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W156" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X156" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y156" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z156" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB156" t="inlineStr"/>
       <c r="AC156" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -43721,12 +43721,12 @@
       </c>
       <c r="AH156" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI156" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ156" t="inlineStr">
@@ -43736,127 +43736,127 @@
       </c>
       <c r="AK156" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/15, 0 HR</t>
+          <t>Last 7 games: 6/25, 0 HR</t>
         </is>
       </c>
       <c r="AL156" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.4% barrel, 5.2 HR allowed</t>
         </is>
       </c>
       <c r="AM156" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN156" t="inlineStr">
         <is>
-          <t>8.04</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="AO156" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>33.71</t>
         </is>
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>88.49</t>
+          <t>86.92</t>
         </is>
       </c>
       <c r="AQ156" t="inlineStr">
         <is>
-          <t>98.7956</t>
+          <t>97.5781</t>
         </is>
       </c>
       <c r="AR156" t="inlineStr">
         <is>
-          <t>0.4017</t>
+          <t>0.3717</t>
         </is>
       </c>
       <c r="AS156" t="inlineStr">
         <is>
-          <t>0.1531</t>
+          <t>0.0931</t>
         </is>
       </c>
       <c r="AT156" t="inlineStr">
         <is>
-          <t>0.3177</t>
+          <t>0.3136</t>
         </is>
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>67.58</t>
         </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>33.02</t>
+          <t>33.59</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>32.18</t>
+          <t>18.29</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>0.1184</t>
+          <t>0.103</t>
         </is>
       </c>
       <c r="BA156" t="inlineStr">
         <is>
-          <t>8.74</t>
+          <t>7.36</t>
         </is>
       </c>
       <c r="BB156" t="inlineStr">
         <is>
-          <t>38.93</t>
+          <t>40.97</t>
         </is>
       </c>
       <c r="BC156" t="inlineStr">
         <is>
-          <t>88.52</t>
+          <t>88.58</t>
         </is>
       </c>
       <c r="BD156" t="inlineStr">
         <is>
-          <t>0.3994</t>
+          <t>0.3567</t>
         </is>
       </c>
       <c r="BE156" t="inlineStr">
         <is>
-          <t>0.1634</t>
+          <t>0.1344</t>
         </is>
       </c>
       <c r="BF156" t="inlineStr">
         <is>
-          <t>30.87</t>
+          <t>27.02</t>
         </is>
       </c>
       <c r="BG156" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH156" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BI156" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Rogers Centre</t>
         </is>
       </c>
       <c r="BJ156" t="inlineStr"/>
@@ -55767,27 +55767,27 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>676391</t>
+          <t>694371</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Ernie Clement</t>
+          <t>Tommy Troy</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>2026-06-13T19:07:00Z</t>
+          <t>2026-06-13T20:10:00Z</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -55797,17 +55797,17 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>Cam Schlittler</t>
+          <t>Rhett Lowder</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>693645</t>
+          <t>695076</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -55834,57 +55834,53 @@
         </is>
       </c>
       <c r="P200" t="n">
-        <v>7.2</v>
+        <v>22.7</v>
       </c>
       <c r="Q200" t="n">
-        <v>33.1</v>
+        <v>40.2</v>
       </c>
       <c r="R200" t="n">
-        <v>68.90000000000001</v>
+        <v>61.3</v>
       </c>
       <c r="S200" t="n">
-        <v>86.40000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T200" t="n">
         <v>50</v>
       </c>
       <c r="U200" t="n">
-        <v>61.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="V200" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W200" t="inlineStr">
+      <c r="W200" t="inlineStr"/>
+      <c r="X200" t="inlineStr"/>
+      <c r="Y200" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z200" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X200" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y200" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z200" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA200" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB200" t="inlineStr"/>
+      <c r="AB200" t="inlineStr">
+        <is>
+          <t>not found on RotoWire</t>
+        </is>
+      </c>
       <c r="AC200" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD200" t="inlineStr"/>
@@ -55901,27 +55897,27 @@
       </c>
       <c r="AH200" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI200" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK200" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/22, 0 HR</t>
         </is>
       </c>
       <c r="AL200" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.4% barrel, 5.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.1% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM200" t="inlineStr">
@@ -55931,112 +55927,112 @@
       </c>
       <c r="AN200" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AO200" t="inlineStr">
         <is>
-          <t>25.44</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>85.69</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AQ200" t="inlineStr">
         <is>
-          <t>95.3697</t>
+          <t>97.6142</t>
         </is>
       </c>
       <c r="AR200" t="inlineStr">
         <is>
-          <t>0.3513</t>
+          <t>0.383</t>
         </is>
       </c>
       <c r="AS200" t="inlineStr">
         <is>
-          <t>0.0958</t>
+          <t>0.148</t>
         </is>
       </c>
       <c r="AT200" t="inlineStr">
         <is>
-          <t>0.2778</t>
+          <t>0.325</t>
         </is>
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>67.67</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AV200" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>26.78</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>0.1483</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="BA200" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="BB200" t="inlineStr">
         <is>
-          <t>40.97</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="BC200" t="inlineStr">
         <is>
-          <t>88.58</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="BD200" t="inlineStr">
         <is>
-          <t>0.3567</t>
+          <t>0.419</t>
         </is>
       </c>
       <c r="BE200" t="inlineStr">
         <is>
-          <t>0.1344</t>
+          <t>0.149</t>
         </is>
       </c>
       <c r="BF200" t="inlineStr">
         <is>
-          <t>27.02</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="BG200" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH200" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BI200" t="inlineStr">
         <is>
-          <t>Rogers Centre</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BJ200" t="inlineStr"/>
@@ -56047,27 +56043,27 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>694371</t>
+          <t>676391</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Tommy Troy</t>
+          <t>Ernie Clement</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>2026-06-13T20:10:00Z</t>
+          <t>2026-06-13T19:07:00Z</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -56077,17 +56073,17 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>Rhett Lowder</t>
+          <t>Cam Schlittler</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>695076</t>
+          <t>693645</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
@@ -56096,7 +56092,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>40.3</v>
+        <v>40.2</v>
       </c>
       <c r="M201" t="inlineStr">
         <is>
@@ -56114,53 +56110,57 @@
         </is>
       </c>
       <c r="P201" t="n">
-        <v>22.7</v>
+        <v>7.2</v>
       </c>
       <c r="Q201" t="n">
-        <v>40.2</v>
+        <v>33.1</v>
       </c>
       <c r="R201" t="n">
-        <v>61.3</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="S201" t="n">
-        <v>64.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T201" t="n">
         <v>50</v>
       </c>
       <c r="U201" t="n">
-        <v>9.300000000000001</v>
+        <v>61.5</v>
       </c>
       <c r="V201" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W201" t="inlineStr"/>
-      <c r="X201" t="inlineStr"/>
+      <c r="W201" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X201" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="Y201" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z201" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z201" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA201" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB201" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB201" t="inlineStr"/>
       <c r="AC201" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD201" t="inlineStr"/>
@@ -56177,27 +56177,27 @@
       </c>
       <c r="AH201" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI201" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/22, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL201" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.1% barrel, 2.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.4% barrel, 5.2 HR allowed</t>
         </is>
       </c>
       <c r="AM201" t="inlineStr">
@@ -56207,112 +56207,112 @@
       </c>
       <c r="AN201" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="AO201" t="inlineStr">
         <is>
-          <t>28.2</t>
+          <t>25.44</t>
         </is>
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>85.69</t>
         </is>
       </c>
       <c r="AQ201" t="inlineStr">
         <is>
-          <t>97.6142</t>
+          <t>95.3697</t>
         </is>
       </c>
       <c r="AR201" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>0.3513</t>
         </is>
       </c>
       <c r="AS201" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>0.0958</t>
         </is>
       </c>
       <c r="AT201" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>0.2778</t>
         </is>
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>67.67</t>
         </is>
       </c>
       <c r="AV201" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>28.2</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>26.78</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.1483</t>
         </is>
       </c>
       <c r="BA201" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>7.36</t>
         </is>
       </c>
       <c r="BB201" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>40.97</t>
         </is>
       </c>
       <c r="BC201" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>88.58</t>
         </is>
       </c>
       <c r="BD201" t="inlineStr">
         <is>
-          <t>0.419</t>
+          <t>0.3567</t>
         </is>
       </c>
       <c r="BE201" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>0.1344</t>
         </is>
       </c>
       <c r="BF201" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>27.02</t>
         </is>
       </c>
       <c r="BG201" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH201" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BI201" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Rogers Centre</t>
         </is>
       </c>
       <c r="BJ201" t="inlineStr"/>
@@ -58283,52 +58283,52 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>641555</t>
+          <t>514888</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>J.C. Escarra</t>
+          <t>Jose Altuve</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>2026-06-13T19:07:00Z</t>
+          <t>2026-06-13T23:10:00Z</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>Kevin Gausman</t>
+          <t>Noah Cameron</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>592332</t>
+          <t>702070</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L209" t="n">
@@ -58346,58 +58346,62 @@
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P209" t="n">
-        <v>18.8</v>
+        <v>16.5</v>
       </c>
       <c r="Q209" t="n">
-        <v>39.7</v>
+        <v>42.1</v>
       </c>
       <c r="R209" t="n">
-        <v>68.90000000000001</v>
+        <v>23.2</v>
       </c>
       <c r="S209" t="n">
-        <v>44.8</v>
+        <v>88.7</v>
       </c>
       <c r="T209" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U209" t="n">
-        <v>0</v>
+        <v>20.8</v>
       </c>
       <c r="V209" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X209" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y209" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W209" t="inlineStr">
+      <c r="Z209" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X209" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y209" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z209" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB209" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB209" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC209" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -58417,27 +58421,27 @@
       </c>
       <c r="AH209" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI209" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AJ209" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AI209" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AJ209" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK209" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/15, 0 HR</t>
+          <t>Last 7 games: 3/22, 1 HR</t>
         </is>
       </c>
       <c r="AL209" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.4% barrel, 12.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.4% barrel, 9.6 HR allowed</t>
         </is>
       </c>
       <c r="AM209" t="inlineStr">
@@ -58447,112 +58451,104 @@
       </c>
       <c r="AN209" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>5.85</t>
         </is>
       </c>
       <c r="AO209" t="inlineStr">
         <is>
-          <t>35.4</t>
+          <t>33.42</t>
         </is>
       </c>
       <c r="AP209" t="inlineStr">
         <is>
-          <t>89.54</t>
+          <t>85.66</t>
         </is>
       </c>
       <c r="AQ209" t="inlineStr">
         <is>
-          <t>99.2378</t>
+          <t>97.6463</t>
         </is>
       </c>
       <c r="AR209" t="inlineStr">
         <is>
-          <t>0.3231</t>
+          <t>0.3602</t>
         </is>
       </c>
       <c r="AS209" t="inlineStr">
         <is>
-          <t>0.1076</t>
+          <t>0.1218</t>
         </is>
       </c>
       <c r="AT209" t="inlineStr">
         <is>
-          <t>0.2727</t>
+          <t>0.3007</t>
         </is>
       </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>70.77</t>
+          <t>69.21</t>
         </is>
       </c>
       <c r="AV209" t="inlineStr">
         <is>
-          <t>10.93</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>34.46</t>
+          <t>46.83</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>17.72</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>0.0995</t>
+          <t>0.1483</t>
         </is>
       </c>
       <c r="BA209" t="inlineStr">
         <is>
-          <t>8.36</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="BB209" t="inlineStr">
         <is>
-          <t>38.81</t>
+          <t>39.92</t>
         </is>
       </c>
       <c r="BC209" t="inlineStr">
         <is>
-          <t>88.46</t>
+          <t>89.02</t>
         </is>
       </c>
       <c r="BD209" t="inlineStr">
         <is>
-          <t>0.3993</t>
+          <t>0.4198</t>
         </is>
       </c>
       <c r="BE209" t="inlineStr">
         <is>
-          <t>0.1592</t>
+          <t>0.1688</t>
         </is>
       </c>
       <c r="BF209" t="inlineStr">
         <is>
-          <t>25.88</t>
-        </is>
-      </c>
-      <c r="BG209" t="inlineStr">
-        <is>
-          <t>Out To RF</t>
-        </is>
-      </c>
-      <c r="BH209" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
+          <t>25.96</t>
+        </is>
+      </c>
+      <c r="BG209" t="inlineStr"/>
+      <c r="BH209" t="inlineStr"/>
       <c r="BI209" t="inlineStr">
         <is>
-          <t>Rogers Centre</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ209" t="inlineStr"/>
@@ -58563,56 +58559,56 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>514888</t>
+          <t>641555</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Jose Altuve</t>
+          <t>J.C. Escarra</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>2026-06-13T23:10:00Z</t>
+          <t>2026-06-13T19:07:00Z</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>Noah Cameron</t>
+          <t>Kevin Gausman</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>702070</t>
+          <t>592332</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L210" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="M210" t="inlineStr">
         <is>
@@ -58626,62 +58622,58 @@
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P210" t="n">
-        <v>16.5</v>
+        <v>18.8</v>
       </c>
       <c r="Q210" t="n">
-        <v>42.1</v>
+        <v>39.7</v>
       </c>
       <c r="R210" t="n">
-        <v>23.2</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="S210" t="n">
-        <v>88.7</v>
+        <v>44.8</v>
       </c>
       <c r="T210" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U210" t="n">
-        <v>20.8</v>
+        <v>0</v>
       </c>
       <c r="V210" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W210" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X210" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y210" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z210" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W210" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X210" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y210" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z210" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB210" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB210" t="inlineStr"/>
       <c r="AC210" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -58701,27 +58693,27 @@
       </c>
       <c r="AH210" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI210" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK210" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/22, 1 HR</t>
+          <t>Last 7 games: 1/15, 0 HR</t>
         </is>
       </c>
       <c r="AL210" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.4% barrel, 9.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.4% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM210" t="inlineStr">
@@ -58731,104 +58723,112 @@
       </c>
       <c r="AN210" t="inlineStr">
         <is>
-          <t>5.85</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AO210" t="inlineStr">
         <is>
-          <t>33.42</t>
+          <t>35.4</t>
         </is>
       </c>
       <c r="AP210" t="inlineStr">
         <is>
-          <t>85.66</t>
+          <t>89.54</t>
         </is>
       </c>
       <c r="AQ210" t="inlineStr">
         <is>
-          <t>97.6463</t>
+          <t>99.2378</t>
         </is>
       </c>
       <c r="AR210" t="inlineStr">
         <is>
-          <t>0.3602</t>
+          <t>0.3231</t>
         </is>
       </c>
       <c r="AS210" t="inlineStr">
         <is>
-          <t>0.1218</t>
+          <t>0.1076</t>
         </is>
       </c>
       <c r="AT210" t="inlineStr">
         <is>
-          <t>0.3007</t>
+          <t>0.2727</t>
         </is>
       </c>
       <c r="AU210" t="inlineStr">
         <is>
-          <t>69.21</t>
+          <t>70.77</t>
         </is>
       </c>
       <c r="AV210" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>10.93</t>
         </is>
       </c>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>46.83</t>
+          <t>34.46</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>17.72</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>0.1483</t>
+          <t>0.0995</t>
         </is>
       </c>
       <c r="BA210" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.36</t>
         </is>
       </c>
       <c r="BB210" t="inlineStr">
         <is>
-          <t>39.92</t>
+          <t>38.81</t>
         </is>
       </c>
       <c r="BC210" t="inlineStr">
         <is>
-          <t>89.02</t>
+          <t>88.46</t>
         </is>
       </c>
       <c r="BD210" t="inlineStr">
         <is>
-          <t>0.4198</t>
+          <t>0.3993</t>
         </is>
       </c>
       <c r="BE210" t="inlineStr">
         <is>
-          <t>0.1688</t>
+          <t>0.1592</t>
         </is>
       </c>
       <c r="BF210" t="inlineStr">
         <is>
-          <t>25.96</t>
-        </is>
-      </c>
-      <c r="BG210" t="inlineStr"/>
-      <c r="BH210" t="inlineStr"/>
+          <t>25.88</t>
+        </is>
+      </c>
+      <c r="BG210" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH210" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI210" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Rogers Centre</t>
         </is>
       </c>
       <c r="BJ210" t="inlineStr"/>
@@ -61536,7 +61536,7 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>37.9</v>
+        <v>37.7</v>
       </c>
       <c r="M221" t="inlineStr">
         <is>
@@ -61560,7 +61560,7 @@
         <v>39.7</v>
       </c>
       <c r="R221" t="n">
-        <v>68.90000000000001</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="S221" t="n">
         <v>64.3</v>
@@ -61751,7 +61751,7 @@
       </c>
       <c r="BH221" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BI221" t="inlineStr">
@@ -65927,47 +65927,47 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>665926</t>
+          <t>608324</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Andrés Giménez</t>
+          <t>Alex Bregman</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>2026-06-13T19:07:00Z</t>
+          <t>2026-06-14T02:05:00Z</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>Cam Schlittler</t>
+          <t>Trevor McDonald</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>693645</t>
+          <t>686790</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
@@ -65976,7 +65976,7 @@
         </is>
       </c>
       <c r="L237" t="n">
-        <v>35.4</v>
+        <v>35.3</v>
       </c>
       <c r="M237" t="inlineStr">
         <is>
@@ -65990,58 +65990,62 @@
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P237" t="n">
-        <v>6.5</v>
+        <v>26.9</v>
       </c>
       <c r="Q237" t="n">
-        <v>33.1</v>
+        <v>21.3</v>
       </c>
       <c r="R237" t="n">
-        <v>68.90000000000001</v>
+        <v>19.3</v>
       </c>
       <c r="S237" t="n">
-        <v>44.8</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T237" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U237" t="n">
-        <v>29.7</v>
+        <v>24.3</v>
       </c>
       <c r="V237" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W237" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X237" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y237" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W237" t="inlineStr">
+      <c r="Z237" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X237" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y237" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z237" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA237" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB237" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB237" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC237" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -66061,27 +66065,27 @@
       </c>
       <c r="AH237" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI237" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/22, 0 HR</t>
+          <t>Last 7 games: 4/25, 1 HR</t>
         </is>
       </c>
       <c r="AL237" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.4% barrel, 5.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 3.9% barrel, 2.4 HR allowed</t>
         </is>
       </c>
       <c r="AM237" t="inlineStr">
@@ -66091,112 +66095,104 @@
       </c>
       <c r="AN237" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="AO237" t="inlineStr">
         <is>
-          <t>24.83</t>
+          <t>40.41</t>
         </is>
       </c>
       <c r="AP237" t="inlineStr">
         <is>
-          <t>86.09</t>
+          <t>88.77</t>
         </is>
       </c>
       <c r="AQ237" t="inlineStr">
         <is>
-          <t>95.7604</t>
+          <t>98.6791</t>
         </is>
       </c>
       <c r="AR237" t="inlineStr">
         <is>
-          <t>0.3232</t>
+          <t>0.3913</t>
         </is>
       </c>
       <c r="AS237" t="inlineStr">
         <is>
-          <t>0.0929</t>
+          <t>0.1425</t>
         </is>
       </c>
       <c r="AT237" t="inlineStr">
         <is>
-          <t>0.2758</t>
+          <t>0.3209</t>
         </is>
       </c>
       <c r="AU237" t="inlineStr">
         <is>
-          <t>68.32</t>
+          <t>70.16</t>
         </is>
       </c>
       <c r="AV237" t="inlineStr">
         <is>
-          <t>4.72</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>36.77</t>
+          <t>46.86</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>22.74</t>
+          <t>23.87</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>0.1226</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BA237" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="BB237" t="inlineStr">
         <is>
-          <t>40.97</t>
+          <t>39.93</t>
         </is>
       </c>
       <c r="BC237" t="inlineStr">
         <is>
-          <t>88.58</t>
+          <t>89.65</t>
         </is>
       </c>
       <c r="BD237" t="inlineStr">
         <is>
-          <t>0.3567</t>
+          <t>0.3557</t>
         </is>
       </c>
       <c r="BE237" t="inlineStr">
         <is>
-          <t>0.1344</t>
+          <t>0.1094</t>
         </is>
       </c>
       <c r="BF237" t="inlineStr">
         <is>
-          <t>27.02</t>
-        </is>
-      </c>
-      <c r="BG237" t="inlineStr">
-        <is>
-          <t>Out To RF</t>
-        </is>
-      </c>
-      <c r="BH237" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
+          <t>11.7</t>
+        </is>
+      </c>
+      <c r="BG237" t="inlineStr"/>
+      <c r="BH237" t="inlineStr"/>
       <c r="BI237" t="inlineStr">
         <is>
-          <t>Rogers Centre</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BJ237" t="inlineStr"/>
@@ -66207,47 +66203,47 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>608324</t>
+          <t>665926</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Alex Bregman</t>
+          <t>Andrés Giménez</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>2026-06-14T02:05:00Z</t>
+          <t>2026-06-13T19:07:00Z</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>Trevor McDonald</t>
+          <t>Cam Schlittler</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>686790</t>
+          <t>693645</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
@@ -66256,7 +66252,7 @@
         </is>
       </c>
       <c r="L238" t="n">
-        <v>35.3</v>
+        <v>35.2</v>
       </c>
       <c r="M238" t="inlineStr">
         <is>
@@ -66270,62 +66266,58 @@
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P238" t="n">
-        <v>26.9</v>
+        <v>6.5</v>
       </c>
       <c r="Q238" t="n">
-        <v>21.3</v>
+        <v>33.1</v>
       </c>
       <c r="R238" t="n">
-        <v>19.3</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="S238" t="n">
-        <v>90.40000000000001</v>
+        <v>44.8</v>
       </c>
       <c r="T238" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U238" t="n">
-        <v>24.3</v>
+        <v>29.7</v>
       </c>
       <c r="V238" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W238" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X238" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y238" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z238" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W238" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X238" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y238" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z238" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA238" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB238" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB238" t="inlineStr"/>
       <c r="AC238" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -66345,27 +66337,27 @@
       </c>
       <c r="AH238" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI238" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ238" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK238" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/25, 1 HR</t>
+          <t>Last 7 games: 7/22, 0 HR</t>
         </is>
       </c>
       <c r="AL238" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 3.9% barrel, 2.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.4% barrel, 5.2 HR allowed</t>
         </is>
       </c>
       <c r="AM238" t="inlineStr">
@@ -66375,104 +66367,112 @@
       </c>
       <c r="AN238" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="AO238" t="inlineStr">
         <is>
-          <t>40.41</t>
+          <t>24.83</t>
         </is>
       </c>
       <c r="AP238" t="inlineStr">
         <is>
-          <t>88.77</t>
+          <t>86.09</t>
         </is>
       </c>
       <c r="AQ238" t="inlineStr">
         <is>
-          <t>98.6791</t>
+          <t>95.7604</t>
         </is>
       </c>
       <c r="AR238" t="inlineStr">
         <is>
-          <t>0.3913</t>
+          <t>0.3232</t>
         </is>
       </c>
       <c r="AS238" t="inlineStr">
         <is>
-          <t>0.1425</t>
+          <t>0.0929</t>
         </is>
       </c>
       <c r="AT238" t="inlineStr">
         <is>
-          <t>0.3209</t>
+          <t>0.2758</t>
         </is>
       </c>
       <c r="AU238" t="inlineStr">
         <is>
-          <t>70.16</t>
+          <t>68.32</t>
         </is>
       </c>
       <c r="AV238" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>46.86</t>
+          <t>36.77</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>23.87</t>
+          <t>22.74</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>0.1226</t>
         </is>
       </c>
       <c r="BA238" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>7.36</t>
         </is>
       </c>
       <c r="BB238" t="inlineStr">
         <is>
-          <t>39.93</t>
+          <t>40.97</t>
         </is>
       </c>
       <c r="BC238" t="inlineStr">
         <is>
-          <t>89.65</t>
+          <t>88.58</t>
         </is>
       </c>
       <c r="BD238" t="inlineStr">
         <is>
-          <t>0.3557</t>
+          <t>0.3567</t>
         </is>
       </c>
       <c r="BE238" t="inlineStr">
         <is>
-          <t>0.1094</t>
+          <t>0.1344</t>
         </is>
       </c>
       <c r="BF238" t="inlineStr">
         <is>
-          <t>11.7</t>
-        </is>
-      </c>
-      <c r="BG238" t="inlineStr"/>
-      <c r="BH238" t="inlineStr"/>
+          <t>27.02</t>
+        </is>
+      </c>
+      <c r="BG238" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH238" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI238" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>Rogers Centre</t>
         </is>
       </c>
       <c r="BJ238" t="inlineStr"/>
@@ -78474,7 +78474,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>62.8</v>
+        <v>62.6</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -78498,7 +78498,7 @@
         <v>39.7</v>
       </c>
       <c r="R11" t="n">
-        <v>68.90000000000001</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="S11" t="n">
         <v>93.2</v>
@@ -78689,7 +78689,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
